--- a/backend/sample.xlsx
+++ b/backend/sample.xlsx
@@ -423,7 +423,7 @@
     <from>
       <col>10</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
